--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129324115</v>
+        <v>129321445</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1465,14 +1465,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506495</v>
+        <v>506645</v>
       </c>
       <c r="R9" t="n">
-        <v>6708133</v>
+        <v>6708359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,12 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tall, förröjd yta stora enso snitslar.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129321445</v>
+        <v>129324115</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1577,14 +1572,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506645</v>
+        <v>506495</v>
       </c>
       <c r="R10" t="n">
-        <v>6708359</v>
+        <v>6708133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1621,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På tall, förröjd yta stora enso snitslar.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129321445</v>
+        <v>129324115</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1465,14 +1465,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506645</v>
+        <v>506495</v>
       </c>
       <c r="R9" t="n">
-        <v>6708359</v>
+        <v>6708133</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tall, förröjd yta stora enso snitslar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129324115</v>
+        <v>129321445</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1572,14 +1577,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506495</v>
+        <v>506645</v>
       </c>
       <c r="R10" t="n">
-        <v>6708133</v>
+        <v>6708359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På tall, förröjd yta stora enso snitslar.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129324222</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129321451</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129321439</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129324448</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129324430</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323880</v>
+        <v>129321457</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506637</v>
+        <v>506643</v>
       </c>
       <c r="R7" t="n">
-        <v>6708248</v>
+        <v>6708354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129321457</v>
+        <v>129323880</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506643</v>
+        <v>506637</v>
       </c>
       <c r="R8" t="n">
-        <v>6708354</v>
+        <v>6708248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129321445</v>
+        <v>129324115</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,14 +1465,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506645</v>
+        <v>506495</v>
       </c>
       <c r="R9" t="n">
-        <v>6708359</v>
+        <v>6708133</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tall, förröjd yta stora enso snitslar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129324115</v>
+        <v>129321445</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,14 +1577,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506495</v>
+        <v>506645</v>
       </c>
       <c r="R10" t="n">
-        <v>6708133</v>
+        <v>6708359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På tall, förröjd yta stora enso snitslar.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,7 @@
         <v>129324377</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129324222</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129321451</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129321439</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129324448</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129324430</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129321457</v>
+        <v>129323880</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506643</v>
+        <v>506637</v>
       </c>
       <c r="R7" t="n">
-        <v>6708354</v>
+        <v>6708248</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323880</v>
+        <v>129321457</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506637</v>
+        <v>506643</v>
       </c>
       <c r="R8" t="n">
-        <v>6708248</v>
+        <v>6708354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129324115</v>
+        <v>129321445</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,14 +1465,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506495</v>
+        <v>506645</v>
       </c>
       <c r="R9" t="n">
-        <v>6708133</v>
+        <v>6708359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,12 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tall, förröjd yta stora enso snitslar.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129321445</v>
+        <v>129324115</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,14 +1572,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506645</v>
+        <v>506495</v>
       </c>
       <c r="R10" t="n">
-        <v>6708359</v>
+        <v>6708133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1621,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På tall, förröjd yta stora enso snitslar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,7 @@
         <v>129324377</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129321445</v>
+        <v>129324115</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1465,14 +1465,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506645</v>
+        <v>506495</v>
       </c>
       <c r="R9" t="n">
-        <v>6708359</v>
+        <v>6708133</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tall, förröjd yta stora enso snitslar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129324115</v>
+        <v>129321445</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1572,14 +1577,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506495</v>
+        <v>506645</v>
       </c>
       <c r="R10" t="n">
-        <v>6708133</v>
+        <v>6708359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På tall, förröjd yta stora enso snitslar.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129324115</v>
+        <v>129321445</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1465,14 +1465,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506495</v>
+        <v>506645</v>
       </c>
       <c r="R9" t="n">
-        <v>6708133</v>
+        <v>6708359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,12 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tall, förröjd yta stora enso snitslar.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129321445</v>
+        <v>129324115</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1577,14 +1572,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506645</v>
+        <v>506495</v>
       </c>
       <c r="R10" t="n">
-        <v>6708359</v>
+        <v>6708133</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1621,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På tall, förröjd yta stora enso snitslar.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323880</v>
+        <v>129321457</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1251,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506637</v>
+        <v>506643</v>
       </c>
       <c r="R7" t="n">
-        <v>6708248</v>
+        <v>6708354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129321457</v>
+        <v>129323880</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506643</v>
+        <v>506637</v>
       </c>
       <c r="R8" t="n">
-        <v>6708354</v>
+        <v>6708248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129321457</v>
+        <v>129323880</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1251,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506643</v>
+        <v>506637</v>
       </c>
       <c r="R7" t="n">
-        <v>6708354</v>
+        <v>6708248</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323880</v>
+        <v>129321457</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506637</v>
+        <v>506643</v>
       </c>
       <c r="R8" t="n">
-        <v>6708248</v>
+        <v>6708354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129324222</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129321451</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129321439</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129324448</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129324430</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129323880</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129321457</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129321445</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129324115</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129324377</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129324222</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129321451</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129321439</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129324448</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129324430</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323880</v>
+        <v>129321457</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506637</v>
+        <v>506643</v>
       </c>
       <c r="R7" t="n">
-        <v>6708248</v>
+        <v>6708354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129321457</v>
+        <v>129323880</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506643</v>
+        <v>506637</v>
       </c>
       <c r="R8" t="n">
-        <v>6708354</v>
+        <v>6708248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>129321445</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129324115</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129324377</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129324222</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129321451</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129321439</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129324448</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129324430</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129321457</v>
+        <v>129323880</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506643</v>
+        <v>506637</v>
       </c>
       <c r="R7" t="n">
-        <v>6708354</v>
+        <v>6708248</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323880</v>
+        <v>129321457</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506637</v>
+        <v>506643</v>
       </c>
       <c r="R8" t="n">
-        <v>6708248</v>
+        <v>6708354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>129321445</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129324115</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129324377</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129321439</v>
+        <v>129324448</v>
       </c>
       <c r="B4" t="n">
         <v>79076</v>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506637</v>
+        <v>506502</v>
       </c>
       <c r="R4" t="n">
-        <v>6708350</v>
+        <v>6708268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129324448</v>
+        <v>129321439</v>
       </c>
       <c r="B5" t="n">
         <v>79076</v>
@@ -1027,14 +1032,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506502</v>
+        <v>506637</v>
       </c>
       <c r="R5" t="n">
-        <v>6708268</v>
+        <v>6708350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,12 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Draperad tall.</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129324222</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129321451</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129324448</v>
+        <v>129321439</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506502</v>
+        <v>506637</v>
       </c>
       <c r="R4" t="n">
-        <v>6708268</v>
+        <v>6708350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Draperad tall.</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129321439</v>
+        <v>129324448</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506637</v>
+        <v>506502</v>
       </c>
       <c r="R5" t="n">
-        <v>6708350</v>
+        <v>6708268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
         <v>129324430</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129323880</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129321457</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129321445</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129324115</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129324377</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129324222</v>
+        <v>129321439</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506513</v>
+        <v>506637</v>
       </c>
       <c r="R2" t="n">
-        <v>6708149</v>
+        <v>6708350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129321451</v>
+        <v>129321445</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -820,7 +820,7 @@
         <v>506645</v>
       </c>
       <c r="R3" t="n">
-        <v>6708357</v>
+        <v>6708359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129321439</v>
+        <v>129321451</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506637</v>
+        <v>506645</v>
       </c>
       <c r="R4" t="n">
-        <v>6708350</v>
+        <v>6708357</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129324448</v>
+        <v>129321457</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506502</v>
+        <v>506643</v>
       </c>
       <c r="R5" t="n">
-        <v>6708268</v>
+        <v>6708354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Draperad tall.</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129324430</v>
+        <v>129323880</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1139,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506483</v>
+        <v>506637</v>
       </c>
       <c r="R6" t="n">
-        <v>6708288</v>
+        <v>6708248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Draperad tall.</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323880</v>
+        <v>129324115</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506637</v>
+        <v>506495</v>
       </c>
       <c r="R7" t="n">
-        <v>6708248</v>
+        <v>6708133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1290,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På tall, förröjd yta stora enso snitslar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,14 +1322,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129321457</v>
+        <v>129324175</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1358,14 +1353,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506643</v>
+        <v>506504</v>
       </c>
       <c r="R8" t="n">
-        <v>6708354</v>
+        <v>6708196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,14 +1429,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129321445</v>
+        <v>129324200</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1465,14 +1460,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506645</v>
+        <v>506493</v>
       </c>
       <c r="R9" t="n">
-        <v>6708359</v>
+        <v>6708169</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,14 +1536,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129324115</v>
+        <v>129324201</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506495</v>
+        <v>506494</v>
       </c>
       <c r="R10" t="n">
-        <v>6708133</v>
+        <v>6708163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,12 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På tall, förröjd yta stora enso snitslar.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,14 +1643,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129324377</v>
+        <v>129324212</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1684,14 +1674,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506479</v>
+        <v>506491</v>
       </c>
       <c r="R11" t="n">
-        <v>6708274</v>
+        <v>6708157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,6 +1747,775 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129324222</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>506513</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6708149</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129324250</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>506495</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6708192</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129324377</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>506479</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6708274</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129324430</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>506483</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6708288</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Draperad tall.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129324448</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>506502</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6708268</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Draperad tall.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129323930</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>506612</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6708195</v>
+      </c>
+      <c r="S17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129324205</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>506492</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6708159</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43914-2024 artfynd.xlsx
+++ b/artfynd/A 43914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324115</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324175</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324200</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324201</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324212</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324222</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324250</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324377</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324430</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324448</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324205</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1971,6 +2031,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321439</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321445</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321451</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321457</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2399,6 +2479,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323880</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2516,8 +2601,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323930</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>